--- a/GRAMMAR/9_18_07.xlsx
+++ b/GRAMMAR/9_18_07.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -464,10 +464,15 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -481,6 +486,11 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -498,6 +508,11 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.011</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -515,10 +530,15 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -532,6 +552,11 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,6 +574,11 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,6 +596,11 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,6 +618,11 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -600,10 +640,15 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -617,6 +662,11 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -634,10 +684,15 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -651,6 +706,11 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -668,10 +728,15 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -685,6 +750,11 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -702,6 +772,11 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -719,6 +794,11 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -740,6 +820,11 @@
           <t>"かまわない"没关系；不在乎</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -757,6 +842,11 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -774,6 +864,11 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -791,6 +886,11 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -808,10 +908,15 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -825,6 +930,11 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -842,6 +952,11 @@
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -859,10 +974,15 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -876,10 +996,15 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -893,6 +1018,11 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -914,6 +1044,11 @@
           <t>"ようにする"设法做到</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -931,10 +1066,15 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -948,6 +1088,11 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -965,6 +1110,11 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -982,6 +1132,11 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -999,10 +1154,15 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1016,10 +1176,15 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1033,6 +1198,11 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1050,6 +1220,11 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1067,10 +1242,15 @@
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1084,6 +1264,11 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
